--- a/data/seed/portfolio/L-2025-2690/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-2690/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J174"/>
+  <dimension ref="A1:J162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -542,75 +542,75 @@
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>14885000</v>
+        <v>11360000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nihol Moy MChJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>303733338</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000700227466001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Shartnoma №43/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по дог. №129/26, НДС 12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>65885000</v>
+        <v>62360000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n">
-        <v>3699000</v>
+        <v>3708000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Shartnoma №103/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6262 01.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>69584000</v>
+        <v>66068000</v>
       </c>
     </row>
     <row r="10">
@@ -622,35 +622,35 @@
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>3018000</v>
+        <v>3189000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Shartnoma №272/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartn. №202/26, QQS 12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>72602000</v>
+        <v>69257000</v>
       </c>
     </row>
     <row r="11">
@@ -662,61 +662,61 @@
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>2647000</v>
+        <v>2578000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olmaliq Non MChJ</t>
+          <t>Farovon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>216809096</t>
+          <t>284797942</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000842591461001</t>
+          <t>20208000349115050001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6697</t>
+          <t>Mahsulot uchun to'lov, shartnoma №116/26, QQS 12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>75249000</v>
+        <v>71835000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>1858000</v>
+        <v>4963000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Meva-Sabzavot MChJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>376773963</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000623939040001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -726,51 +726,51 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SHARTNOMA №194/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Shartnoma №241/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>77107000</v>
+        <v>76798000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>1271000</v>
+        <v>2766000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Shartnoma №20/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №16/26 от 03.07.2026</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>78378000</v>
+        <v>79564000</v>
       </c>
     </row>
     <row r="14">
@@ -782,35 +782,35 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>7817000</v>
+        <v>2641000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Farovon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>284797942</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000349115050001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8723 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №98/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>86195000</v>
+        <v>82205000</v>
       </c>
     </row>
     <row r="15">
@@ -820,23 +820,23 @@
       <c r="B15" t="n">
         <v>107</v>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n">
-        <v>6868000</v>
-      </c>
+      <c r="C15" s="2" t="n">
+        <v>1259000</v>
+      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Guliston Tur Servis AJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>335538466</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000051923428001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -846,11 +846,11 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5040</t>
+          <t>Оплата за сырье по договору №109/26 от 06.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>93063000</v>
+        <v>80946000</v>
       </c>
     </row>
     <row r="16">
@@ -860,37 +860,37 @@
       <c r="B16" t="n">
         <v>108</v>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n">
-        <v>2476000</v>
-      </c>
+      <c r="C16" s="2" t="n">
+        <v>3939000</v>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Afrosiyob Metall Servis MChJ</t>
+          <t>Afrosiyob Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>320847979</t>
+          <t>351306652</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000213491150001</t>
+          <t>20208000836420932001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №199/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №226/26, QQS bilan</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>95539000</v>
+        <v>77007000</v>
       </c>
     </row>
     <row r="17">
@@ -901,151 +901,151 @@
         <v>109</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1730000</v>
+        <v>8267000</v>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yulduz Avto Ehtiyot AJ</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>294377679</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000249014378001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №154/26 от 06.07.2026, НДС 12%</t>
+          <t>Iyun oyi uchun ish haqi, reestr №7215</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>93809000</v>
+        <v>68740000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>1814000</v>
-      </c>
-      <c r="D18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n">
+        <v>6679000</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Namangan Logistik MChJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>346264682</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000604418317001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №226/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №293/26, НДС 12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>91995000</v>
+        <v>75419000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>8267000</v>
+        <v>1334000</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Qo'qon Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>258859578</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000202425962001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>IYUN OYI UCHUN ISH HAQI, REESTR №955</t>
+          <t>Аренда помещения за июль, дог. №55/20</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>83728000</v>
+        <v>74085000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>85084000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>2289000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Yulduz Avto Ehtiyot AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>294377679</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000249014378001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №109/26 от 06.07.2026, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6793</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-1356000</v>
+        <v>76374000</v>
       </c>
     </row>
     <row r="21">
@@ -1055,37 +1055,37 @@
       <c r="B21" t="n">
         <v>113</v>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>1334000</v>
-      </c>
-      <c r="D21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n">
+        <v>1441000</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>362588595</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000832024259001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov iyul</t>
+          <t>Shartnoma №265/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-2690000</v>
+        <v>77815000</v>
       </c>
     </row>
     <row r="22">
@@ -1096,22 +1096,22 @@
         <v>114</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>15959000</v>
+        <v>8591000</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Qarshi Logistik XK</t>
+          <t>Qarshi Mebel MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>246174653</t>
+          <t>317465392</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000291605404001</t>
+          <t>20208000160540423001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-18649000</v>
+        <v>69224000</v>
       </c>
     </row>
     <row r="23">
@@ -1135,37 +1135,37 @@
       <c r="B23" t="n">
         <v>115</v>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>9201000</v>
-      </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n">
+        <v>1955000</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Yulduz Avto Ehtiyot AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>294377679</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000249014378001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №230/26</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №4849 10.07.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-27850000</v>
+        <v>71179000</v>
       </c>
     </row>
     <row r="24">
@@ -1175,112 +1175,112 @@
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>13900000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>1661000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-2690)</t>
+          <t>Nihol Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>16307000331327338417</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-2690 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7683 10.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-41750000</v>
+        <v>72840000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>13638000</v>
+        <v>1210000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8122 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6696</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>-28112000</v>
+        <v>74050000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>2288000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>13900000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olmaliq Non MChJ</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>216809096</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-2690)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000842591461001</t>
+          <t>16307000331327338417</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №167/26, QQS 12%</t>
+          <t>Kredit shartnomasi L-2025-2690 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-25824000</v>
+        <v>60150000</v>
       </c>
     </row>
     <row r="27">
@@ -1292,21 +1292,21 @@
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>1687000</v>
+        <v>17857000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Samarqand Farm Savdo MChJ</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>359418499</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000048601438001</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1316,11 +1316,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №272/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №262/26, QQS 12%</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>-24137000</v>
+        <v>78007000</v>
       </c>
     </row>
     <row r="28">
@@ -1332,35 +1332,35 @@
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>1293000</v>
+        <v>11816000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №209/26, НДС 12%</t>
+          <t>Shartnoma №82/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>-22844000</v>
+        <v>89823000</v>
       </c>
     </row>
     <row r="29">
@@ -1370,23 +1370,23 @@
       <c r="B29" t="n">
         <v>121</v>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>2203000</v>
-      </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n">
+        <v>1391000</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Farg'ona Mehmonxona AJ</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>219363075</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000900785176001</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1396,11 +1396,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №78/26, QQS bilan</t>
+          <t>Оплата по счет-фактуре №9759 за поставленный товар</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>-25047000</v>
+        <v>91214000</v>
       </c>
     </row>
     <row r="30">
@@ -1410,23 +1410,23 @@
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>5187000</v>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n">
+        <v>1366000</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kamalak Mehmonxona AJ</t>
+          <t>Samarqand Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>261259829</t>
+          <t>273333887</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000209446162001</t>
+          <t>20208000022746625001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1436,11 +1436,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №101/26</t>
+          <t>Mahsulot uchun to'lov, shartn. №139/26, QQS 12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>-30234000</v>
+        <v>92580000</v>
       </c>
     </row>
     <row r="31">
@@ -1451,36 +1451,36 @@
         <v>123</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>5315000</v>
+        <v>6945000</v>
       </c>
       <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Qarshi Logistik XK</t>
+          <t>Qo'qon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>246174653</t>
+          <t>225982902</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000291605404001</t>
+          <t>20208000944616207001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №1864</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №86/26</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>-35549000</v>
+        <v>85635000</v>
       </c>
     </row>
     <row r="32">
@@ -1491,36 +1491,36 @@
         <v>124</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>7697000</v>
+        <v>134125000</v>
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Farg'ona Mehmonxona AJ</t>
+          <t>Saodat Trans Servis XK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>219363075</t>
+          <t>364835440</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000900785176001</t>
+          <t>20208000610673676001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №86/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №101/26</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>-43246000</v>
+        <v>-48490000</v>
       </c>
     </row>
     <row r="33">
@@ -1530,157 +1530,157 @@
       <c r="B33" t="n">
         <v>125</v>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n">
-        <v>4363000</v>
-      </c>
+      <c r="C33" s="2" t="n">
+        <v>1127000</v>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Afrosiyob Metall Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>320847979</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000213491150001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Shartnoma №173/26 bo'yicha oldindan to'lov</t>
+          <t>Iyun oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>-38883000</v>
+        <v>-49617000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n">
-        <v>4340000</v>
-      </c>
+      <c r="C34" s="2" t="n">
+        <v>1127000</v>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olmaliq Non MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>216809096</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000842591461001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №26/26, QQS 12%</t>
+          <t>JShDS iyun oyi uchun</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>-34543000</v>
+        <v>-50744000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>1127000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>6243000</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июнь</t>
+          <t>Предоплата за товар по договору №100/26 от 16.07.2026</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>-35670000</v>
+        <v>-44501000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>1127000</v>
-      </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n">
+        <v>3728000</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Jismony shaxslar daromad solig'i iyun 2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4344 16.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>-36797000</v>
+        <v>-40773000</v>
       </c>
     </row>
     <row r="37">
@@ -1692,35 +1692,35 @@
       </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n">
-        <v>32934000</v>
+        <v>2662000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOA №46/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №121/26, НДС 12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>-3863000</v>
+        <v>-38111000</v>
       </c>
     </row>
     <row r="38">
@@ -1732,35 +1732,35 @@
       </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n">
-        <v>1769000</v>
+        <v>1240000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Olmaliq Non MChJ</t>
+          <t>Farovon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>216809096</t>
+          <t>284797942</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000842591461001</t>
+          <t>20208000349115050001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOM №9/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2841 16.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>-2094000</v>
+        <v>-36871000</v>
       </c>
     </row>
     <row r="39">
@@ -1770,23 +1770,23 @@
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>1362000</v>
-      </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n">
+        <v>3133000</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Farg'ona Mehmonxona AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>219363075</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000900785176001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1796,77 +1796,77 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №8/26</t>
+          <t>Оплата по счет-фактуре №4088 за поставленный товар</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>-3456000</v>
+        <v>-33738000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46223</v>
+        <v>46220</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n">
-        <v>20902000</v>
+        <v>2261000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Afrosiyob Metall Servis MChJ</t>
+          <t>Saodat Mehmonxona XK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>320847979</t>
+          <t>377396346</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000213491150001</t>
+          <t>20208000393904022001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №78/26, QQS 12%</t>
+          <t>Преоплата за товар по договору №3/26 от 17.07.2026</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>17446000</v>
+        <v>-31477000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46223</v>
+        <v>46220</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>1796000</v>
-      </c>
-      <c r="D41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n">
+        <v>2115000</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Farg'ona Mehmonxona AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>219363075</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000900785176001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1876,237 +1876,237 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №53/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4298 17.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>15650000</v>
+        <v>-29362000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46223</v>
+        <v>46220</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>7530000</v>
-      </c>
-      <c r="D42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n">
+        <v>2041000</v>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Jizzax Yog'och XK</t>
+          <t>Denov Sut AJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>296355384</t>
+          <t>237767972</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000630519234001</t>
+          <t>20208000901437891001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №189/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8367</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>8120000</v>
+        <v>-27321000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46224</v>
+        <v>46220</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>13831000</v>
+        <v>1820000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nihol Moy MChJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>303733338</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000700227466001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №214/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6353</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>21951000</v>
+        <v>-25501000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46224</v>
+        <v>46220</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n">
-        <v>3091000</v>
-      </c>
+      <c r="C44" s="2" t="n">
+        <v>916000</v>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Meva-Sabzavot MChJ</t>
+          <t>Farovon Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>376773963</t>
+          <t>326468216</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000623939040001</t>
+          <t>20208000441831795001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Shartnoma №55/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за транспортные услуги по договору №189/26</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>25042000</v>
+        <v>-26417000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
-      <c r="C45" s="2" t="n">
-        <v>2193000</v>
-      </c>
-      <c r="D45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n">
+        <v>3160000</v>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>НДС за июнь 2026 г.</t>
+          <t>Оплата по с/ф №2638 за поставленный товар</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>22849000</v>
+        <v>-23257000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>3668000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>1957000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Qo'qon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>225982902</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000944616207001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №22/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №53/26</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>26517000</v>
+        <v>-25214000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>1761000</v>
-      </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n">
+        <v>28147000</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Farg'ona Mehmonxona AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>219363075</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000900785176001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2116,131 +2116,131 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №164/26, QQS bilan</t>
+          <t>Shartnoma №198/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>24756000</v>
+        <v>2933000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46226</v>
+        <v>46224</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n">
-        <v>3699000</v>
-      </c>
+      <c r="C48" s="2" t="n">
+        <v>2246000</v>
+      </c>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Afrosiyob Metall Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>320847979</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000213491150001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9777</t>
+          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>28455000</v>
+        <v>687000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>1452000</v>
+        <v>2952000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Urganch Tikuv MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>382297300</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000639934522001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3133 за поставленный товар</t>
+          <t>Mahsulot uchun to'lov, shartn. №96/26, QQS 12%</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>29907000</v>
+        <v>3639000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n">
-        <v>2618000</v>
-      </c>
-      <c r="D50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n">
+        <v>1104000</v>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Yulduz Avto Ehtiyot AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>294377679</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000249014378001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №228/26, QQS bilan</t>
+          <t>Tovar uchun to'lov, h/f №4640 22.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>27289000</v>
+        <v>4743000</v>
       </c>
     </row>
     <row r="51">
@@ -2250,117 +2250,117 @@
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>834000</v>
-      </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n">
+        <v>5868000</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000208287755001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov iyul</t>
+          <t>Tovar uchun to'lov, h/f №8084 24.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>26455000</v>
+        <v>10611000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n">
-        <v>6615000</v>
+        <v>5651000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №250/26, QQS 12%</t>
+          <t>TOVAR UCHUN TO'LOV, H/F №9490 24.07.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>33070000</v>
+        <v>16262000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>5074000</v>
+        <v>1220000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Olmaliq Non MChJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>216809096</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000842591461001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8644</t>
+          <t>Shartnoma №254/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>38144000</v>
+        <v>17482000</v>
       </c>
     </row>
     <row r="54">
@@ -2372,21 +2372,21 @@
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>1944000</v>
+        <v>12716000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Samarqand Farm Savdo MChJ</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>359418499</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000048601438001</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2396,11 +2396,11 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №191/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №148/26, QQS 12%</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>40088000</v>
+        <v>30198000</v>
       </c>
     </row>
     <row r="55">
@@ -2410,23 +2410,23 @@
       <c r="B55" t="n">
         <v>147</v>
       </c>
-      <c r="C55" s="2" t="n">
-        <v>1165000</v>
-      </c>
-      <c r="D55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n">
+        <v>11651000</v>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Afrosiyob Qog'oz MChJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>272221687</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000974378314001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2436,11 +2436,11 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №122/26, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6435 27.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>38923000</v>
+        <v>41849000</v>
       </c>
     </row>
     <row r="56">
@@ -2450,37 +2450,37 @@
       <c r="B56" t="n">
         <v>148</v>
       </c>
-      <c r="C56" s="2" t="n">
-        <v>1175000</v>
-      </c>
-      <c r="D56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n">
+        <v>4335000</v>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kamalak Mehmonxona AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>261259829</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000209446162001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6951</t>
+          <t>Mahsulot uchun to'lov, shartn. №147/26, QQS 12%</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>37748000</v>
+        <v>46184000</v>
       </c>
     </row>
     <row r="57">
@@ -2490,23 +2490,23 @@
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>2410000</v>
-      </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n">
+        <v>3160000</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Farg'ona Mehmonxona AJ</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>219363075</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000900785176001</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2516,37 +2516,37 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8880</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8612 27.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>35338000</v>
+        <v>49344000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>5809000</v>
+        <v>1587000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Saodat Mehmonxona XK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>377396346</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000393904022001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2556,131 +2556,131 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6669 28.07.2026, QQS bilan</t>
+          <t>Shartnoma №173/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>41147000</v>
+        <v>50931000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n">
-        <v>3733000</v>
-      </c>
+      <c r="C59" s="2" t="n">
+        <v>834000</v>
+      </c>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000828775508001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №1629</t>
+          <t>Elektr energiyasi uchun to'lov iyul</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>44880000</v>
+        <v>50097000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n">
-        <v>1599000</v>
-      </c>
+      <c r="C60" s="2" t="n">
+        <v>878000</v>
+      </c>
+      <c r="D60" s="2" t="n"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Nukus Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>271584027</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000636119525001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №297/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №122/26, QQS bilan</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>46479000</v>
+        <v>49219000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n">
-        <v>2007000</v>
-      </c>
-      <c r="D61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n">
+        <v>1512000</v>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Yulduz Avto Ehtiyot AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>294377679</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000249014378001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №154/26</t>
+          <t>Mahulot uchun to'lov, shartnoma №126/26, QQS 12%</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>44472000</v>
+        <v>50731000</v>
       </c>
     </row>
     <row r="62">
@@ -2690,178 +2690,178 @@
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n">
-        <v>2389000</v>
-      </c>
+      <c r="C62" s="2" t="n">
+        <v>1021000</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Qo'qon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>225982902</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000944616207001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №15/26, НДС 12%</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №1214</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>46861000</v>
+        <v>49710000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>2372000</v>
+        <v>300000</v>
       </c>
       <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Farg'ona Mehmonxona AJ</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>219363075</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000900785176001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №1214</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>44489000</v>
+        <v>49410000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>2131000</v>
+        <v>1745000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, H/F №4349 30.07.2026, QQS BILAN</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5228</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>46620000</v>
+        <v>51155000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46234</v>
+        <v>46239</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
-      <c r="C65" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n">
+        <v>12825000</v>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Qo'qon Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Mahsulot uchun to'lov, shartnoma №175/26, QQS 12%</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>46320000</v>
+        <v>63980000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>3322000</v>
+        <v>3968000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Meva-Sabzavot MChJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>376773963</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000623939040001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2871,312 +2871,312 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3301 за поставленный товар</t>
+          <t>Mahsulot uchun to'lov, sharnoma №3/26, QQS 12%</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>49642000</v>
+        <v>67948000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n">
-        <v>2159000</v>
+        <v>800000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №931</t>
+          <t>Предоплата за товар по договору №101/26 от 05.08.2026</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>51801000</v>
+        <v>68748000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>39480000</v>
+        <v>8843000</v>
       </c>
       <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Afrosiyob Qog'oz MChJ</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>272221687</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000974378314001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №299/26 от 03.08.2026, НДС 12%</t>
+          <t>ЗАРАБОТНАЯ ПЛАТА ЗА ИЮЛЬ 2026 Г. (ПЕРЕЧИСЛЕНИЕ НА ПЛАСТИКОВЫЕ КАРТЫ)</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>12321000</v>
+        <v>59905000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n">
-        <v>17326000</v>
-      </c>
+      <c r="C69" s="2" t="n">
+        <v>13428000</v>
+      </c>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Qo'qon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>306087419</t>
+          <t>225982902</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000868972089001</t>
+          <t>20208000944616207001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Shartnoma №155/26 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №194/26</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>29647000</v>
+        <v>46477000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n">
-        <v>4402000</v>
-      </c>
+      <c r="C70" s="2" t="n">
+        <v>15376000</v>
+      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Saodat Trans Servis XK</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>364835440</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000610673676001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №275/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №118/26, QQS bilan</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>34049000</v>
+        <v>31101000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>8843000</v>
-      </c>
-      <c r="D71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n">
+        <v>3259000</v>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Qo'qon Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ish haqi, reestr №1810</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4498</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>25206000</v>
+        <v>34360000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n">
-        <v>27209000</v>
+        <v>3042000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, sharnoma №3/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, h/f №7866 07.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>52415000</v>
+        <v>37402000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n">
-        <v>5608000</v>
-      </c>
+      <c r="C73" s="2" t="n">
+        <v>1427000</v>
+      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Qo'qon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>258859578</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000202425962001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №175/26, QQS 12%</t>
+          <t>Ijara haqi avgust oyi uchun, shartnoma №55/20</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>58023000</v>
+        <v>35975000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>2619000</v>
+        <v>1849000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Samarqand Farm Savdo MChJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>359418499</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000048601438001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3186,131 +3186,131 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7446</t>
+          <t>Mahsulot uchun to'lov, shartn. №241/26, QQS 12%</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>60642000</v>
+        <v>37824000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>2544000</v>
+        <v>1611000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Shartnoma №120/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №163/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>63186000</v>
+        <v>39435000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
       <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="n">
-        <v>3722000</v>
+        <v>1598000</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4498</t>
+          <t>Mahsulot uchun to'lov, shartnoma №135/26, QQS 12%</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>66908000</v>
+        <v>41033000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
       <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="n">
-        <v>3333000</v>
+        <v>1105000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Olmaliq Non MChJ</t>
+          <t>Yulduz Tikuv MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>216809096</t>
+          <t>341849930</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000842591461001</t>
+          <t>20208000860143896001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №7866 07.08.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1369</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>70241000</v>
+        <v>42138000</v>
       </c>
     </row>
     <row r="78">
@@ -3320,143 +3320,138 @@
       <c r="B78" t="n">
         <v>170</v>
       </c>
-      <c r="C78" s="2" t="n"/>
-      <c r="D78" s="2" t="n">
-        <v>8582000</v>
-      </c>
+      <c r="C78" s="2" t="n">
+        <v>13900000</v>
+      </c>
+      <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Olmaliq Non MChJ</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>216809096</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-2690)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000842591461001</t>
+          <t>16307000331327338417</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №876</t>
+          <t>Kredit shartnomasi L-2025-2690 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>78823000</v>
+        <v>28238000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n">
-        <v>6559000</v>
+        <v>1138000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №135/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6147</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>85382000</v>
+        <v>29376000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>2974000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>15504000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Afrosiyob Metall Servis MChJ</t>
+          <t>Qo'qon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>320847979</t>
+          <t>225982902</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000213491150001</t>
+          <t>20208000944616207001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Shartnoma №40/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за упаковочные материалы, с/ф №8935</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>88356000</v>
+        <v>13872000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>2747000</v>
+        <v>2413000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Omad Oziq-ovqat Savdo XK</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>312964425</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000074286218001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3466,472 +3461,477 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Shartnoma №8/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №278/26, QQS 12%</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>91103000</v>
+        <v>16285000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n">
-        <v>2164000</v>
+        <v>1458000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Shartnoma №163/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №280/26, QQS 12%</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>93267000</v>
+        <v>17743000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>1493000</v>
+        <v>2033000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Nihol Moy MChJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>303733338</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000700227466001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №272/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №7813 от 14.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>94760000</v>
+        <v>19776000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>1427000</v>
-      </c>
-      <c r="D84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n">
+        <v>989000</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish AJ</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>362588595</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000832024259001</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Арендная плата за август 2026г. по договору №83/23</t>
+          <t>Оплата за товар по счет-фактуре №6523 от 14.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>93333000</v>
+        <v>20765000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>13900000</v>
-      </c>
-      <c r="D85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n">
+        <v>59701000</v>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-2690)</t>
+          <t>Samarqand Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>273333887</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>16307000331327338417</t>
+          <t>20208000022746625001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-2690 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Предоплата за товар по дог. №220/26 от 17.08.2026</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>79433000</v>
+        <v>80466000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46245</v>
+        <v>46251</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>2221000</v>
+        <v>6352000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Olmaliq Non MChJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>216809096</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000842591461001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №278/26 от 11.08.2026</t>
+          <t>Shartnoma №225/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>81654000</v>
+        <v>86818000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>5908000</v>
-      </c>
-      <c r="D87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n">
+        <v>4644000</v>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Kamalak Mehmonxona AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>261259829</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000209446162001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №54/26</t>
+          <t>SHARTNOMA №43/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>75746000</v>
+        <v>91462000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>9864000</v>
+        <v>1206000</v>
       </c>
       <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Farg'ona Mehmonxona AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>219363075</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000900785176001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTN. №212/26</t>
+          <t>Iyul oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>65882000</v>
+        <v>90256000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n">
-        <v>5361000</v>
-      </c>
+      <c r="C89" s="2" t="n">
+        <v>1206000</v>
+      </c>
+      <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №46/26, QQS 12%</t>
+          <t>Jismoniy shaxslar daromad solig'i iyul 2026</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>71243000</v>
+        <v>89050000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>12400000</v>
+        <v>10381000</v>
       </c>
       <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Qarshi Logistik XK</t>
+          <t>Qo'qon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>246174653</t>
+          <t>225982902</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000291605404001</t>
+          <t>20208000944616207001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №263/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №273/26</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>58843000</v>
+        <v>78669000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n">
-        <v>10576000</v>
-      </c>
+      <c r="C91" s="2" t="n">
+        <v>22241000</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Samarqand Farm Savdo MChJ</t>
+          <t>Afrosiyob Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>359418499</t>
+          <t>351306652</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000048601438001</t>
+          <t>20208000836420932001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2352</t>
+          <t>Предоплата за материалы по договору №157/26</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>69419000</v>
+        <v>56428000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>1404000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>51272000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Olmaliq Non MChJ</t>
+          <t>Qo'qon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>216809096</t>
+          <t>225982902</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000842591461001</t>
+          <t>20208000944616207001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6523 от 14.08.2026, в т.ч. НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №221/26, QQS bilan</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>70823000</v>
+        <v>5156000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
       <c r="C93" s="2" t="n"/>
       <c r="D93" s="2" t="n">
-        <v>3430000</v>
+        <v>1862000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Saodat Mehmonxona XK</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>377396346</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000393904022001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3941,157 +3941,157 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1355 17.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по дог. №14/26 от 18.08.2026</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>74253000</v>
+        <v>7018000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
-      <c r="C94" s="2" t="n">
-        <v>1206000</v>
-      </c>
-      <c r="D94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n">
+        <v>1426000</v>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ijtimoiy soliq</t>
+          <t>Shartnoma №255/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>73047000</v>
+        <v>8444000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
-      <c r="C95" s="2" t="n">
-        <v>1206000</v>
-      </c>
-      <c r="D95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n">
+        <v>11965000</v>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Denov Sut AJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>237767972</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000901437891001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>НДФЛ за июль 2026</t>
+          <t>Shartnoma №220/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>71841000</v>
+        <v>20409000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>4097000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>1644000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Farg'ona Mehmonxona AJ</t>
+          <t>Yangi Hayot Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>219363075</t>
+          <t>308741948</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000900785176001</t>
+          <t>20208000897208985001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №166</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6044 19.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>67744000</v>
+        <v>22053000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>9934000</v>
-      </c>
-      <c r="D97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n">
+        <v>13284000</v>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Farg'ona Mehmonxona AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>219363075</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000900785176001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4101,157 +4101,157 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №244/26, QQS BILAN</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №6218 20.08.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>57810000</v>
+        <v>35337000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="n">
-        <v>4110000</v>
+        <v>7829000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Yulduz Tikuv MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>341849930</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000860143896001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov shartnoma №245/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №159/26, НДС 12%</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>61920000</v>
+        <v>43166000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n">
-        <v>3353000</v>
+        <v>1211000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Farovon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>284797942</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000349115050001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5822</t>
+          <t>Оплата за товар по с/ф №1455 от 21.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>65273000</v>
+        <v>44377000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46252</v>
+        <v>46258</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="n">
-        <v>2009000</v>
+        <v>11654000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Shartnoma №255/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №244/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>67282000</v>
+        <v>56031000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>5396000</v>
+        <v>1347000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Afrosiyob Metall Servis MChJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>320847979</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000213491150001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4261,437 +4261,437 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №63/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №75/26, НДС 12%</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>72678000</v>
+        <v>57378000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n">
-        <v>2357000</v>
-      </c>
+      <c r="C102" s="2" t="n">
+        <v>892000</v>
+      </c>
+      <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000828775508001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Shartnoma №112/26 bo'yicha oldindan to'lov</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>75035000</v>
+        <v>56486000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n">
-        <v>2176000</v>
-      </c>
+      <c r="C103" s="2" t="n">
+        <v>2289000</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Shartnoma №258/26 bo'yicha oldindan to'lov</t>
+          <t>QQS iyul 2026 uchun</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>77211000</v>
+        <v>54197000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n">
-        <v>1336000</v>
-      </c>
+      <c r="C104" s="2" t="n">
+        <v>33447000</v>
+      </c>
+      <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Omad Oziq-ovqat Savdo XK</t>
+          <t>Qo'qon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>312964425</t>
+          <t>225982902</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000074286218001</t>
+          <t>20208000944616207001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №18/26, QQS 12%</t>
+          <t>Tovarlar uchun to'lov h/f №1820</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>78547000</v>
+        <v>20750000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n">
-        <v>7675000</v>
+        <v>1939000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №44/26 от 20.08.2026</t>
+          <t>Shartnoma №96/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>86222000</v>
+        <v>22689000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
       <c r="C106" s="2" t="n"/>
       <c r="D106" s="2" t="n">
-        <v>2890000</v>
+        <v>10793000</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Samarqand Farm Savdo MChJ</t>
+          <t>Olmaliq Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>359418499</t>
+          <t>296442540</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000048601438001</t>
+          <t>20208000428621896001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №159/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №9086 за поставленный товар</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>89112000</v>
+        <v>33482000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>52822000</v>
-      </c>
-      <c r="D107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n">
+        <v>2269000</v>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kamalak Mehmonxona AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>261259829</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000209446162001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №296/26 от 20.08.2026, НДС 12%</t>
+          <t>Shartnoma №120/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>36290000</v>
+        <v>35751000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
-      <c r="C108" s="2" t="n"/>
-      <c r="D108" s="2" t="n">
-        <v>934000</v>
-      </c>
+      <c r="C108" s="2" t="n">
+        <v>8927000</v>
+      </c>
+      <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Samarqand Farm Savdo MChJ</t>
+          <t>Qo'qon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>359418499</t>
+          <t>225982902</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000048601438001</t>
+          <t>20208000944616207001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Shartnoma №101/26 bo'yicha oldindan to'lov</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №118/26</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>37224000</v>
+        <v>26824000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>2384000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>1295000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3369 28.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>34840000</v>
+        <v>28119000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>3066000</v>
+        <v>5539000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №75/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №53/26, QQS 12%</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>37906000</v>
+        <v>33658000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n">
-        <v>2498000</v>
+        <v>3175000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Denov Sut AJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>237767972</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000901437891001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Shartnoma №114/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №211/26, QQS 12%</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>40404000</v>
+        <v>36833000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="n">
-        <v>1926000</v>
+        <v>1559000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bahor Savdo MChJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>306087419</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000868972089001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4701,37 +4701,37 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №121/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №220/26, QQS 12%</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>42330000</v>
+        <v>38392000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
       <c r="C113" s="2" t="n"/>
       <c r="D113" s="2" t="n">
-        <v>1080000</v>
+        <v>1412000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Omad Oziq-ovqat Savdo XK</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>312964425</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000074286218001</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4741,277 +4741,272 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №232/26, QQS 12%</t>
+          <t>Shartnoma №24/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>43410000</v>
+        <v>39804000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>8753000</v>
+        <v>300000</v>
       </c>
       <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Farg'ona Mehmonxona AJ</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>219363075</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000900785176001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №21/26</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>34657000</v>
+        <v>39504000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
       <c r="C115" s="2" t="n"/>
       <c r="D115" s="2" t="n">
-        <v>7483000</v>
+        <v>11561000</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Olmaliq Non MChJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>216809096</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000842591461001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9167 25.08.2026, QQS bilan</t>
+          <t>SHARTNOMA №61/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>42140000</v>
+        <v>51065000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>6273000</v>
+        <v>7392000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Farovon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>284797942</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000349115050001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3050</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4235</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>48413000</v>
+        <v>58457000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>1304000</v>
+        <v>2519000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Urganch Tikuv MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>382297300</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000639934522001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №339 25.08.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2510</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>49717000</v>
+        <v>60976000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>892000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>1851000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000208287755001</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4102 01.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>48825000</v>
+        <v>62827000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46259</v>
+        <v>46268</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
-      <c r="C119" s="2" t="n">
-        <v>4276000</v>
-      </c>
-      <c r="D119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n">
+        <v>5181000</v>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Yulduz Avto Ehtiyot AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>294377679</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000249014378001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №50/26, QQS bilan</t>
+          <t>Оплата по с/ф №5987 за поставленный товар</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>44549000</v>
+        <v>68008000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46262</v>
+        <v>46268</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>2176000</v>
+        <v>2451000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Meva-Sabzavot MChJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>376773963</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000623939040001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5021,77 +5016,77 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №8485 28.08.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №7164 от 03.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>46725000</v>
+        <v>70459000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46262</v>
+        <v>46268</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
       <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="n">
-        <v>2049000</v>
+        <v>2443000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Denov Sut AJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>237767972</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000901437891001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №154/26 от 28.08.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №77/26, QQS 12%</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>48774000</v>
+        <v>72902000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46262</v>
+        <v>46268</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>12181000</v>
-      </c>
-      <c r="D122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n">
+        <v>2027000</v>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Kamalak Mehmonxona AJ</t>
+          <t>Farovon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>261259829</t>
+          <t>284797942</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000209446162001</t>
+          <t>20208000349115050001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5101,37 +5096,37 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №113/26</t>
+          <t>Оплата по с/ф №6637 за поставленный товар</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>36593000</v>
+        <v>74929000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
       <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="n">
-        <v>12648000</v>
+        <v>2596000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Samarqand Farm Savdo MChJ</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>359418499</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000048601438001</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5141,747 +5136,747 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №257/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №82/26, QQS 12%</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>49241000</v>
+        <v>77525000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>3621000</v>
+        <v>38300000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Denov Sut AJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>237767972</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000901437891001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №53/26, QQS 12%</t>
+          <t>Оплата по с/ф №3780 за поставленный товар</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>52862000</v>
+        <v>115825000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="n">
-        <v>2516000</v>
+        <v>3799000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Farovon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>284797942</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000349115050001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8482</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1306</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>55378000</v>
+        <v>119624000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n">
+        <v>2746000</v>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Nihol Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2534</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>55078000</v>
+        <v>122370000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>9531000</v>
+        <v>1400000</v>
       </c>
       <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Kamalak Mehmonxona AJ</t>
+          <t>Qo'qon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>261259829</t>
+          <t>258859578</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000209446162001</t>
+          <t>20208000202425962001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8914</t>
+          <t>Ijara haqi sentyabr oyi uchun, shartnoma №55/20</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>45547000</v>
+        <v>120970000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46266</v>
+        <v>46272</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
-      <c r="C128" s="2" t="n"/>
-      <c r="D128" s="2" t="n">
-        <v>11784000</v>
-      </c>
+      <c r="C128" s="2" t="n">
+        <v>8671000</v>
+      </c>
+      <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>262908924</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №298/26, QQS 12%</t>
+          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>57331000</v>
+        <v>112299000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>15419000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>8451000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Farg'ona Mehmonxona AJ</t>
+          <t>Farovon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>219363075</t>
+          <t>284797942</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000900785176001</t>
+          <t>20208000349115050001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5045</t>
+          <t>Mahsulot uchun to'lov, shartnoma №81/26, QQS 12%</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>41912000</v>
+        <v>120750000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>7489000</v>
+        <v>7140000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Olmaliq Non MChJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>216809096</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000842591461001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Shartnoma №178/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №90/26 от 09.09.2026</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>49401000</v>
+        <v>127890000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
       <c r="C131" s="2" t="n">
-        <v>4853000</v>
+        <v>13900000</v>
       </c>
       <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Farg'ona Mehmonxona AJ</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>219363075</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-2690)</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000900785176001</t>
+          <t>16307000331327338417</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №6315</t>
+          <t>Kredit shartnomasi L-2025-2690 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>44548000</v>
+        <v>113990000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>44618000</v>
+        <v>7022000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Shartnoma №290/26 bo'yicha oldindan to'lov</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №112/26 ОТ 11.09.2026</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>89166000</v>
+        <v>121012000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n">
-        <v>11544000</v>
+        <v>4439000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2624 04.09.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7979</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>100710000</v>
+        <v>125451000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46269</v>
+        <v>46279</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
       <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="n">
-        <v>3333000</v>
+        <v>9003000</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Denov Sut AJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>237767972</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000901437891001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6994 от 04.09.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №4/26, QQS 12%</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>104043000</v>
+        <v>134454000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46269</v>
+        <v>46279</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n">
-        <v>8671000</v>
-      </c>
-      <c r="D135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n">
+        <v>6141000</v>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Qo'qon Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ish haqi, reestr №6435</t>
+          <t>Предоплата за товар по дог. №219/26 от 14.09.2026</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>95372000</v>
+        <v>140595000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46269</v>
+        <v>46279</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>18879000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>4898000</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Farg'ona Mehmonxona AJ</t>
+          <t>Qo'qon Mato XK</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>219363075</t>
+          <t>267245028</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000900785176001</t>
+          <t>20208000558103175001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №285/26</t>
+          <t>TOVAR UCHUN TO'LOV, H/F №6724 14.09.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>76493000</v>
+        <v>145493000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46269</v>
+        <v>46279</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>23347000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>1839000</v>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Qarshi Logistik XK</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>246174653</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000291605404001</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1207</t>
+          <t>Оплата за товар по счет-фактуре №3151 от 14.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>53146000</v>
+        <v>147332000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
-      <c r="C138" s="2" t="n"/>
-      <c r="D138" s="2" t="n">
-        <v>5857000</v>
-      </c>
+      <c r="C138" s="2" t="n">
+        <v>8592000</v>
+      </c>
+      <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Qo'qon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>225982902</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000944616207001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Shartnoma №93/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по договору №190/26 от 14.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>59003000</v>
+        <v>138740000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46272</v>
+        <v>46280</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n">
-        <v>4466000</v>
-      </c>
+      <c r="C139" s="2" t="n">
+        <v>1182000</v>
+      </c>
+      <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3725 07.09.2026, QQS bilan</t>
+          <t>Avgust oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>63469000</v>
+        <v>137558000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46272</v>
+        <v>46280</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
-      <c r="C140" s="2" t="n"/>
-      <c r="D140" s="2" t="n">
-        <v>3451000</v>
-      </c>
+      <c r="C140" s="2" t="n">
+        <v>1182000</v>
+      </c>
+      <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Afrosiyob Metall Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>320847979</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000213491150001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Shartnoma №282/26 bo'yicha oldindanto'lov</t>
+          <t>НДФЛ за август 2026</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>66920000</v>
+        <v>136376000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46272</v>
+        <v>46280</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
-      <c r="C141" s="2" t="n"/>
-      <c r="D141" s="2" t="n">
-        <v>3309000</v>
-      </c>
+      <c r="C141" s="2" t="n">
+        <v>43012000</v>
+      </c>
+      <c r="D141" s="2" t="n"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Afrosiyob Metall Servis MChJ</t>
+          <t>Guliston Tur Servis AJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>320847979</t>
+          <t>335538466</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000213491150001</t>
+          <t>20208000051923428001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №155/26, НДС 12%</t>
+          <t>Оплата за сырье по договору №84/26 от 15.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>70229000</v>
+        <v>93364000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46273</v>
+        <v>46281</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>1400000</v>
+        <v>7646000</v>
       </c>
       <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish AJ</t>
+          <t>Saodat Trans Servis XK</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>362588595</t>
+          <t>364835440</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000832024259001</t>
+          <t>20208000610673676001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5891,192 +5886,197 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Аренда помещения за сентябрь, дог. №83/23</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №263/26</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>68829000</v>
+        <v>85718000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46274</v>
+        <v>46282</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
-      <c r="C143" s="2" t="n"/>
-      <c r="D143" s="2" t="n">
-        <v>8977000</v>
-      </c>
+      <c r="C143" s="2" t="n">
+        <v>6353000</v>
+      </c>
+      <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Olmaliq Non MChJ</t>
+          <t>Guliston Tur Servis AJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>216809096</t>
+          <t>335538466</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000842591461001</t>
+          <t>20208000051923428001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3288</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №115/26 ОТ 17.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>77806000</v>
+        <v>79365000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
       <c r="C144" s="2" t="n">
-        <v>13900000</v>
+        <v>4936000</v>
       </c>
       <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-2690)</t>
+          <t>Qo'qon Farm Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>225982902</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>16307000331327338417</t>
+          <t>20208000944616207001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-2690 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №166/26</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>63906000</v>
+        <v>74429000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>5502000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>20145000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Afrosiyob Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>351306652</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000836420932001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №1841 от 11.09.2026, в т.ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №253/26</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>69408000</v>
+        <v>54284000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
       <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="n">
-        <v>6907000</v>
+        <v>2292000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6688 14.09.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №198/26, QQS 12%</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>76315000</v>
+        <v>56576000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46279</v>
+        <v>46287</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
-      <c r="C147" s="2" t="n">
-        <v>7771000</v>
-      </c>
-      <c r="D147" s="2" t="n"/>
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n">
+        <v>36155000</v>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Farg'ona Mehmonxona AJ</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>219363075</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000900785176001</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6086,237 +6086,237 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №28/26</t>
+          <t>Shartnoma №250/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>68544000</v>
+        <v>92731000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46279</v>
+        <v>46287</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
       <c r="C148" s="2" t="n">
-        <v>13795000</v>
+        <v>2421000</v>
       </c>
       <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Farg'ona Mehmonxona AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>219363075</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000900785176001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №39/26</t>
+          <t>QQS avgust 2026 uchun</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>54749000</v>
+        <v>90310000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
-      <c r="C149" s="2" t="n"/>
-      <c r="D149" s="2" t="n">
-        <v>9429000</v>
-      </c>
+      <c r="C149" s="2" t="n">
+        <v>4749000</v>
+      </c>
+      <c r="D149" s="2" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Meva-Sabzavot MChJ</t>
+          <t>Guliston Tur Servis AJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>376773963</t>
+          <t>335538466</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000623939040001</t>
+          <t>20208000051923428001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №6917 за поставленный товар</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №237/26</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>64178000</v>
+        <v>85561000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
       <c r="C150" s="2" t="n">
-        <v>1182000</v>
+        <v>39163000</v>
       </c>
       <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Guliston Tur Servis AJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>335538466</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000051923428001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Уплата социального налога за август</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №268/26</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>62996000</v>
+        <v>46398000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
-      <c r="C151" s="2" t="n">
-        <v>1182000</v>
-      </c>
-      <c r="D151" s="2" t="n"/>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="2" t="n">
+        <v>4361000</v>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за август 2026 г.</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6508</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>61814000</v>
+        <v>50759000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46282</v>
+        <v>46289</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
       <c r="C152" s="2" t="n"/>
       <c r="D152" s="2" t="n">
-        <v>7101000</v>
+        <v>3622000</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Denov Sut AJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>262908924</t>
+          <t>237767972</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000638358540001</t>
+          <t>20208000901437891001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №232/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №7940 24.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>68915000</v>
+        <v>54381000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
       <c r="C153" s="2" t="n"/>
       <c r="D153" s="2" t="n">
-        <v>2905000</v>
+        <v>3565000</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Meva-Sabzavot MChJ</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>376773963</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000623939040001</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6326,37 +6326,37 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №165/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №9125 за поставленный товар</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>71820000</v>
+        <v>57946000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
       <c r="C154" s="2" t="n"/>
       <c r="D154" s="2" t="n">
-        <v>4126000</v>
+        <v>4851000</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Samarqand Savdo XK</t>
+          <t>Farovon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>329822973</t>
+          <t>284797942</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000076399345001</t>
+          <t>20208000349115050001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6366,77 +6366,77 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Shartnoma №256/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartn. №176/26, QQS 12%</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>75946000</v>
+        <v>62797000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="B155" t="n">
         <v>247</v>
       </c>
       <c r="C155" s="2" t="n">
-        <v>2332000</v>
+        <v>875000</v>
       </c>
       <c r="D155" s="2" t="n"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000828775508001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>QQS AVGUST 2026 UCHUN</t>
+          <t>Elektr energiyasi uchun to'lov sentyabr</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>73614000</v>
+        <v>61922000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B156" t="n">
         <v>248</v>
       </c>
-      <c r="C156" s="2" t="n">
-        <v>11829000</v>
-      </c>
-      <c r="D156" s="2" t="n"/>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n">
+        <v>7528000</v>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Farg'ona Mehmonxona AJ</t>
+          <t>Nihol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>219363075</t>
+          <t>380909688</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000900785176001</t>
+          <t>20208000259146145001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6446,671 +6446,191 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №220/26</t>
+          <t>Mahsulot uchun to'lov, shartn. №143/26, QQS 12%</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>61785000</v>
+        <v>69450000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
-        <v>46287</v>
+        <v>46293</v>
       </c>
       <c r="B157" t="n">
         <v>249</v>
       </c>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n">
-        <v>19322000</v>
-      </c>
+      <c r="C157" s="2" t="n">
+        <v>35327000</v>
+      </c>
+      <c r="D157" s="2" t="n"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Nihol Moy MChJ</t>
+          <t>Qo'qon Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>303733338</t>
+          <t>225982902</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000700227466001</t>
+          <t>20208000944616207001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7070 22.09.2026, QQS bilan</t>
+          <t>Tovarlar uchun to'lov h/f №8954</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>81107000</v>
+        <v>34123000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="B158" t="n">
         <v>250</v>
       </c>
-      <c r="C158" s="2" t="n">
-        <v>15983000</v>
-      </c>
-      <c r="D158" s="2" t="n"/>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n">
+        <v>3963000</v>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Kamalak Mehmonxona AJ</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>261259829</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000209446162001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3349</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5334</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>65124000</v>
+        <v>38086000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="B159" t="n">
         <v>251</v>
       </c>
-      <c r="C159" s="2" t="n">
-        <v>7653000</v>
-      </c>
-      <c r="D159" s="2" t="n"/>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>3614000</v>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Jizzax Yog'och XK</t>
+          <t>Qo'qon Tekstil MChJ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>296355384</t>
+          <t>290892416</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000630519234001</t>
+          <t>20208000835854018001</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №240/26, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4878</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>57471000</v>
+        <v>41700000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="B160" t="n">
         <v>252</v>
       </c>
-      <c r="C160" s="2" t="n"/>
-      <c r="D160" s="2" t="n">
-        <v>2599000</v>
-      </c>
+      <c r="C160" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D160" s="2" t="n"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Nihol Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>303733338</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000700227466001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8355 24.09.2026, QQS bilan</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>60070000</v>
+        <v>41400000</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B161" t="n">
-        <v>253</v>
-      </c>
-      <c r="C161" s="2" t="n"/>
-      <c r="D161" s="2" t="n">
-        <v>4410000</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Olmaliq Non MChJ</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>216809096</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>20208000842591461001</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartn. №204/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J161" s="2" t="n">
-        <v>64480000</v>
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Итого обороты:</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="n">
+        <v>589259000</v>
+      </c>
+      <c r="D161" s="4" t="n">
+        <v>579659000</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B162" t="n">
-        <v>254</v>
-      </c>
-      <c r="C162" s="2" t="n"/>
-      <c r="D162" s="2" t="n">
-        <v>3848000</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Olmaliq Non MChJ</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>216809096</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>20208000842591461001</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №198/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J162" s="2" t="n">
-        <v>68328000</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B163" t="n">
-        <v>255</v>
-      </c>
-      <c r="C163" s="2" t="n"/>
-      <c r="D163" s="2" t="n">
-        <v>3556000</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Olmaliq Non MChJ</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>216809096</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>20208000842591461001</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3715 28.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J163" s="2" t="n">
-        <v>71884000</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B164" t="n">
-        <v>256</v>
-      </c>
-      <c r="C164" s="2" t="n">
-        <v>875000</v>
-      </c>
-      <c r="D164" s="2" t="n"/>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>20208000208287755001</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
-        </is>
-      </c>
-      <c r="J164" s="2" t="n">
-        <v>71009000</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B165" t="n">
-        <v>257</v>
-      </c>
-      <c r="C165" s="2" t="n">
-        <v>5738000</v>
-      </c>
-      <c r="D165" s="2" t="n"/>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Chirchiq Sut Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>366648354</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>20208000066106736001</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №172/26</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="n">
-        <v>65271000</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B166" t="n">
-        <v>258</v>
-      </c>
-      <c r="C166" s="2" t="n">
-        <v>23795000</v>
-      </c>
-      <c r="D166" s="2" t="n"/>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Nihol Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>327513066</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>20208000258364209001</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по договору №2/26</t>
-        </is>
-      </c>
-      <c r="J166" s="2" t="n">
-        <v>41476000</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B167" t="n">
-        <v>259</v>
-      </c>
-      <c r="C167" s="2" t="n"/>
-      <c r="D167" s="2" t="n">
-        <v>10380000</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Samarqand Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>359418499</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>20208000048601438001</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №32/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J167" s="2" t="n">
-        <v>51856000</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B168" t="n">
-        <v>260</v>
-      </c>
-      <c r="C168" s="2" t="n">
-        <v>15208000</v>
-      </c>
-      <c r="D168" s="2" t="n"/>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Farg'ona Mehmonxona AJ</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>219363075</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>20208000900785176001</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Оплата за упаковочные материалы, с/ф№6438</t>
-        </is>
-      </c>
-      <c r="J168" s="2" t="n">
-        <v>36648000</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B169" t="n">
-        <v>261</v>
-      </c>
-      <c r="C169" s="2" t="n"/>
-      <c r="D169" s="2" t="n">
-        <v>4900000</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Olmaliq Non MChJ</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>216809096</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>20208000842591461001</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №56/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="n">
-        <v>41548000</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B170" t="n">
-        <v>262</v>
-      </c>
-      <c r="C170" s="2" t="n"/>
-      <c r="D170" s="2" t="n">
-        <v>4483000</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Termiz Meva Eksport AJ</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>262908924</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>20208000638358540001</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №1940</t>
-        </is>
-      </c>
-      <c r="J170" s="2" t="n">
-        <v>46031000</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B171" t="n">
-        <v>263</v>
-      </c>
-      <c r="C171" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D171" s="2" t="n"/>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Bodomzor Bank ATB</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>КОМИССИЯ БАНКА ЗА РАСЧЕТНО-КАССОВОЕ ОБСЛУЖИВАНИЕ ЗА СЕНТЯБРЬ</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="n">
-        <v>45731000</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B172" t="n">
-        <v>264</v>
-      </c>
-      <c r="C172" s="2" t="n">
-        <v>4331000</v>
-      </c>
-      <c r="D172" s="2" t="n"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Farg'ona Mehmonxona AJ</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>219363075</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>20208000900785176001</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №259/26</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="n">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Исходящий остаток на 30.09.2026:</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="n">
         <v>41400000</v>
       </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Итого обороты:</t>
-        </is>
-      </c>
-      <c r="C173" s="4" t="n">
-        <v>585315000</v>
-      </c>
-      <c r="D173" s="4" t="n">
-        <v>575715000</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Исходящий остаток на 30.09.2026:</t>
-        </is>
-      </c>
-      <c r="C174" s="4" t="n">
-        <v>41400000</v>
-      </c>
-      <c r="D174" s="4" t="n"/>
+      <c r="D162" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
